--- a/reports/pdf_change_20260904.xlsx
+++ b/reports/pdf_change_20260904.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,425억   ·   현금 24억(0.5%)      당일 2026-09-04  vs  전영업일 2026-09-03      매수 4종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,314억      당일 2026-09-04  vs  전영업일 2026-09-03      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>109</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1310207250</v>
+        <v>1306365000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-46</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3025829400</v>
+        <v>-3016956000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1617669900</v>
+        <v>1612926000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-40</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2815296000</v>
+        <v>-2807040000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3311962500</v>
+        <v>3302250000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-9</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2605581000</v>
+        <v>-2597940000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2993298000</v>
+        <v>2984520000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,652억   ·   현금 12억(0.3%)      당일 2026-09-04  vs  전영업일 2026-09-03      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,530억      당일 2026-09-04  vs  전영업일 2026-09-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -847,7 +847,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,471억   ·   현금 31억(1.3%)      당일 2026-09-04  vs  전영업일 2026-09-03      매수 2종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,410억      당일 2026-09-04  vs  전영업일 2026-09-03      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -943,7 +943,7 @@
         <v>300</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1833108000</v>
+        <v>1835757000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>-71</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1103013400</v>
+        <v>-1104607350</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2314048000</v>
+        <v>2317392000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>-40</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1790896000</v>
+        <v>-1793484000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>-32</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-735180800</v>
+        <v>-736243200</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,065억   ·   현금 25억(1.2%)      당일 2026-09-04  vs  전영업일 2026-09-03      매수 1종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,990억      당일 2026-09-04  vs  전영업일 2026-09-03      매수 1종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1148,7 +1148,7 @@
         <v>19</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1201556200</v>
+        <v>1187336600</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>-119</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-325798200</v>
+        <v>-321942600</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>-44</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-303388800</v>
+        <v>-299798400</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>-26</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-196851200</v>
+        <v>-194521600</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>-13</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-119736500</v>
+        <v>-118319500</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 262억   ·   현금 1억(0.5%)      당일 2026-09-04  vs  전영업일 2026-09-03      매수 3종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 257억      당일 2026-09-04  vs  전영업일 2026-09-03      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1365,11 +1365,11 @@
         <v>47</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>51817500</v>
+        <v>51126600</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>3.29%→3.49%</t>
+          <t>3.31%→3.51%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1386,11 +1386,11 @@
         <v>-52</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-36254400</v>
+        <v>-35271600</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.92%</t>
+          <t>1.05%→0.92%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>68208000</v>
+        <v>67228000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1430,11 +1430,11 @@
         <v>-13</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-18882500</v>
+        <v>-18837000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>5.43%→5.36%</t>
+          <t>5.52%→5.45%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1453,11 +1453,11 @@
         <v>11</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>38577000</v>
+        <v>38153500</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.17%</t>
+          <t>1.03%→1.18%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1474,11 +1474,11 @@
         <v>-6</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-23436000</v>
+        <v>-21798000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>3.28%→3.19%</t>
+          <t>3.11%→3.03%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1502,11 +1502,11 @@
         <v>-5</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-20615000</v>
+        <v>-19845000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>1.79%→1.71%</t>
+          <t>1.76%→1.68%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -1530,11 +1530,11 @@
         <v>-3</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-82425000</v>
+        <v>-80010000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.00%</t>
+          <t>0.31%→0.00%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1546,7 +1546,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 523억   ·   현금 4억(0.9%)      당일 2026-09-04  vs  전영업일 2026-09-03      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 504억      당일 2026-09-04  vs  전영업일 2026-09-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
